--- a/public/题库模板.xlsx
+++ b/public/题库模板.xlsx
@@ -1,53 +1,59 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="题库" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="题库" sheetId="1" r:id="rId1"/>
+    <sheet name="使用说明" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="13"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -55,103 +61,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BBBBBB"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BBBBBB"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BBBBBB"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BBBBBB"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -230,6 +151,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -264,6 +186,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -298,20 +221,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -433,222 +352,327 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M5"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col min="1" max="1" width="46.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="42.83203125" customWidth="1"/>
+    <col min="5" max="5" width="22.83203125" customWidth="1"/>
+    <col min="6" max="6" width="22.83203125" customWidth="1"/>
+    <col min="7" max="7" width="22.83203125" customWidth="1"/>
+    <col min="8" max="8" width="22.83203125" customWidth="1"/>
+    <col min="9" max="9" width="22.83203125" customWidth="1"/>
+    <col min="10" max="10" width="22.83203125" customWidth="1"/>
+    <col min="11" max="11" width="22.83203125" customWidth="1"/>
+    <col min="12" max="12" width="22.83203125" customWidth="1"/>
+    <col min="13" max="13" width="22.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>题干</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>答案</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
+      <c r="A1" t="str">
+        <v>题干</v>
+      </c>
+      <c r="B1" t="str">
+        <v>题型</v>
+      </c>
+      <c r="C1" t="str">
+        <v>答案</v>
+      </c>
+      <c r="D1" t="str">
+        <v>图片地址</v>
+      </c>
+      <c r="E1" t="str">
+        <v>标签</v>
+      </c>
+      <c r="F1" t="str">
+        <v>A</v>
+      </c>
+      <c r="G1" t="str">
+        <v>B</v>
+      </c>
+      <c r="H1" t="str">
+        <v>C</v>
+      </c>
+      <c r="I1" t="str">
+        <v>D</v>
+      </c>
+      <c r="J1" t="str">
+        <v>E</v>
+      </c>
+      <c r="K1" t="str">
+        <v>F</v>
+      </c>
+      <c r="L1" t="str">
+        <v>G</v>
+      </c>
+      <c r="M1" t="str">
+        <v>H</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>示例·单选（填好后删）:依据安规，进入作业现场应正确佩戴（ ）。</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>岗位标识</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>上岗证</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>工作牌</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>安全帽</t>
-        </is>
+      <c r="A2" t="str">
+        <v>示例·单选（填好后删）导线的主要作用是什么？</v>
+      </c>
+      <c r="B2" t="str">
+        <v>单选</v>
+      </c>
+      <c r="C2" t="str">
+        <v>A</v>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v>基础，示例</v>
+      </c>
+      <c r="F2" t="str">
+        <v>传输电能</v>
+      </c>
+      <c r="G2" t="str">
+        <v>装饰线路</v>
+      </c>
+      <c r="H2" t="str">
+        <v>储存电能</v>
+      </c>
+      <c r="I2" t="str">
+        <v>测量温度</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>示例·判断（填好后删）:安全带应高挂低用。（ ）</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>正确</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>错误</t>
-        </is>
+      <c r="A3" t="str">
+        <v>示例·多选（填好后删）安全巡视应做到哪些？</v>
+      </c>
+      <c r="B3" t="str">
+        <v>多选</v>
+      </c>
+      <c r="C3" t="str">
+        <v>AB</v>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v>安全，示例</v>
+      </c>
+      <c r="F3" t="str">
+        <v>佩戴防护用品</v>
+      </c>
+      <c r="G3" t="str">
+        <v>核对线路编号</v>
+      </c>
+      <c r="H3" t="str">
+        <v>跨越警戒区域</v>
+      </c>
+      <c r="I3" t="str">
+        <v>跳过危险点记录</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>示例·判断（填好后删）巡视前应确认天气和现场风险。</v>
+      </c>
+      <c r="B4" t="str">
+        <v>判断</v>
+      </c>
+      <c r="C4" t="str">
+        <v>A</v>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
+        <v>安全，示例</v>
+      </c>
+      <c r="F4" t="str">
+        <v>正确</v>
+      </c>
+      <c r="G4" t="str">
+        <v>错误</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>示例·计算（填好后删）某量计算结果是多少？</v>
+      </c>
+      <c r="B5" t="str">
+        <v>计算</v>
+      </c>
+      <c r="C5" t="str">
+        <v>12.5</v>
+      </c>
+      <c r="D5" t="str">
+        <v>https://example.com/question.png</v>
+      </c>
+      <c r="E5" t="str">
+        <v>计算，示例</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:M5"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B13"/>
   <cols>
-    <col width="90" customWidth="1" min="1" max="1"/>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="110.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>题库模板填写规则</t>
-        </is>
+      <c r="A1" t="str">
+        <v>拾卷 · 题库 Excel 模板使用说明</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="str">
+        <v>适用项目</v>
+      </c>
+      <c r="B2" t="str">
+        <v>拾卷（exam-study-app）本地优先刷题 PWA</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1. 第 1 行是表头，不要改、不要删。数据从第 2 行开始，每行一题。</t>
-        </is>
+      <c r="A3" t="str">
+        <v>导入步骤</v>
+      </c>
+      <c r="B3" t="str">
+        <v>1. 复制本模板；2. 删除题库页全部示例行；3. 按列填写；4. 将文件命名为送电线路工-初级工/中级工/高级工/技师.xlsx；5. 在题库页点击导入 Excel。</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2. 列顺序：A=题干  B=答案  C 起为选项。</t>
-        </is>
+      <c r="A4" t="str">
+        <v>题干</v>
+      </c>
+      <c r="B4" t="str">
+        <v>必填。支持普通文字，以及 $...$ 行内公式和 $$...$$ 独立公式。</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>3. 答案写字母：单选 A；多选 ACD（也可写 A,C,D 或 A、C）。判断题可写「正确」「错误」或 A/B。</t>
-        </is>
+      <c r="A5" t="str">
+        <v>题型</v>
+      </c>
+      <c r="B5" t="str">
+        <v>必填，只能填写：单选、多选、判断、计算。</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>4. 选项个数不限：从 C 列起连续填写，中间不要留空。需要更多选项就往右继续列。</t>
-        </is>
+      <c r="A6" t="str">
+        <v>答案</v>
+      </c>
+      <c r="B6" t="str">
+        <v>单选填一个字母；多选填多个字母（如 AC）；判断填 A/正确 或 B/错误；计算题填标准数值（如 12.5、-3、1e6）。</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>5. 判断题 = 把选项填成 正确 / 错误 两个即可。</t>
-        </is>
+      <c r="A7" t="str">
+        <v>图片地址</v>
+      </c>
+      <c r="B7" t="str">
+        <v>可选。填写完整的 http/https 图片 URL；导入后显示在题干下方。请确保各设备都能访问该地址。</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>6. 题干为空、答案为空/无法识别、答案字母超出选项数 → 该行自动跳过。</t>
-        </is>
+      <c r="A8" t="str">
+        <v>标签</v>
+      </c>
+      <c r="B8" t="str">
+        <v>可选。多个标签使用中文逗号、英文逗号或顿号分隔。</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>7. 文件名即题库名：安规.xlsx → questions/安规.json。模板「题库模板.xlsx」本身会被 build 跳过。</t>
-        </is>
+      <c r="A9" t="str">
+        <v>选项</v>
+      </c>
+      <c r="B9" t="str">
+        <v>单选、多选、判断题从 A 列开始连续填写，不得断列；判断题必须依次为“正确、错误”。计算题不要填写选项。</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>8. 流程：复制本模板 → 改名为 &lt;库名&gt;.xlsx → 填写 → make bank。</t>
-        </is>
+      <c r="A10" t="str">
+        <v>计算题误差</v>
+      </c>
+      <c r="B10" t="str">
+        <v>计算题按配置页中的“计算题允许误差”判定，使用相对误差百分比；标准答案为 0 时按同一百分比折算为绝对误差。</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>图片与离线</v>
+      </c>
+      <c r="B11" t="str">
+        <v>图片 URL 由浏览器加载；题目文字和学习记录仍保存在本机并通过 Sync v5 同步。</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>限制</v>
+      </c>
+      <c r="B12" t="str">
+        <v>单次最多导入 20,000 题；每题最多 24 个选项；Excel 文件最大 12 MB。</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>安全提醒</v>
+      </c>
+      <c r="B13" t="str">
+        <v>不要在工作簿中填写 GitHub 令牌或其他账号凭据。</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B13"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/public/题库模板.xlsx
+++ b/public/题库模板.xlsx
@@ -398,12 +398,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:L5"/>
   <cols>
     <col min="1" max="1" width="46.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
     <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="42.83203125" customWidth="1"/>
+    <col min="4" max="4" width="22.83203125" customWidth="1"/>
     <col min="5" max="5" width="22.83203125" customWidth="1"/>
     <col min="6" max="6" width="22.83203125" customWidth="1"/>
     <col min="7" max="7" width="22.83203125" customWidth="1"/>
@@ -412,7 +412,6 @@
     <col min="10" max="10" width="22.83203125" customWidth="1"/>
     <col min="11" max="11" width="22.83203125" customWidth="1"/>
     <col min="12" max="12" width="22.83203125" customWidth="1"/>
-    <col min="13" max="13" width="22.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -426,33 +425,30 @@
         <v>答案</v>
       </c>
       <c r="D1" t="str">
-        <v>图片地址</v>
+        <v>标签</v>
       </c>
       <c r="E1" t="str">
-        <v>标签</v>
+        <v>A</v>
       </c>
       <c r="F1" t="str">
-        <v>A</v>
+        <v>B</v>
       </c>
       <c r="G1" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="H1" t="str">
-        <v>C</v>
+        <v>D</v>
       </c>
       <c r="I1" t="str">
-        <v>D</v>
+        <v>E</v>
       </c>
       <c r="J1" t="str">
-        <v>E</v>
+        <v>F</v>
       </c>
       <c r="K1" t="str">
-        <v>F</v>
+        <v>G</v>
       </c>
       <c r="L1" t="str">
-        <v>G</v>
-      </c>
-      <c r="M1" t="str">
         <v>H</v>
       </c>
     </row>
@@ -467,21 +463,18 @@
         <v>A</v>
       </c>
       <c r="D2" t="str">
-        <v/>
+        <v>基础，示例</v>
       </c>
       <c r="E2" t="str">
-        <v>基础，示例</v>
+        <v>传输电能</v>
       </c>
       <c r="F2" t="str">
-        <v>传输电能</v>
+        <v>装饰线路</v>
       </c>
       <c r="G2" t="str">
-        <v>装饰线路</v>
+        <v>储存电能</v>
       </c>
       <c r="H2" t="str">
-        <v>储存电能</v>
-      </c>
-      <c r="I2" t="str">
         <v>测量温度</v>
       </c>
     </row>
@@ -496,21 +489,18 @@
         <v>AB</v>
       </c>
       <c r="D3" t="str">
-        <v/>
+        <v>安全，示例</v>
       </c>
       <c r="E3" t="str">
-        <v>安全，示例</v>
+        <v>佩戴防护用品</v>
       </c>
       <c r="F3" t="str">
-        <v>佩戴防护用品</v>
+        <v>核对线路编号</v>
       </c>
       <c r="G3" t="str">
-        <v>核对线路编号</v>
+        <v>跨越警戒区域</v>
       </c>
       <c r="H3" t="str">
-        <v>跨越警戒区域</v>
-      </c>
-      <c r="I3" t="str">
         <v>跳过危险点记录</v>
       </c>
     </row>
@@ -525,15 +515,12 @@
         <v>A</v>
       </c>
       <c r="D4" t="str">
-        <v/>
+        <v>安全，示例</v>
       </c>
       <c r="E4" t="str">
-        <v>安全，示例</v>
+        <v>正确</v>
       </c>
       <c r="F4" t="str">
-        <v>正确</v>
-      </c>
-      <c r="G4" t="str">
         <v>错误</v>
       </c>
     </row>
@@ -548,22 +535,19 @@
         <v>12.5</v>
       </c>
       <c r="D5" t="str">
-        <v>https://example.com/question.png</v>
-      </c>
-      <c r="E5" t="str">
         <v>计算，示例</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B12"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="110.83203125" customWidth="1"/>
@@ -616,63 +600,55 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>图片地址</v>
+        <v>标签</v>
       </c>
       <c r="B7" t="str">
-        <v>可选。填写完整的 http/https 图片 URL；导入后显示在题干下方。请确保各设备都能访问该地址。</v>
+        <v>可选。多个标签使用中文逗号、英文逗号或顿号分隔。</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>标签</v>
+        <v>选项</v>
       </c>
       <c r="B8" t="str">
-        <v>可选。多个标签使用中文逗号、英文逗号或顿号分隔。</v>
+        <v>单选、多选、判断题从 A 列开始连续填写，不得断列；判断题必须依次为“正确、错误”。计算题不要填写选项。</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>选项</v>
+        <v>计算题误差</v>
       </c>
       <c r="B9" t="str">
-        <v>单选、多选、判断题从 A 列开始连续填写，不得断列；判断题必须依次为“正确、错误”。计算题不要填写选项。</v>
+        <v>计算题按配置页中的“计算题允许误差”判定，使用相对误差百分比；标准答案为 0 时按同一百分比折算为绝对误差。</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>计算题误差</v>
+        <v>图片题</v>
       </c>
       <c r="B10" t="str">
-        <v>计算题按配置页中的“计算题允许误差”判定，使用相对误差百分比；标准答案为 0 时按同一百分比折算为绝对误差。</v>
+        <v>Excel 只导入纯文字题。导入后请在题目编辑器中选择本机图片并插入到题干或选项的任意位置；图片会作为私有资产同步。</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>图片与离线</v>
+        <v>限制</v>
       </c>
       <c r="B11" t="str">
-        <v>图片 URL 由浏览器加载；题目文字和学习记录仍保存在本机并通过 Sync v5 同步。</v>
+        <v>单次最多导入 20,000 题；每题最多 24 个选项；Excel 文件最大 12 MB。</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>限制</v>
+        <v>安全提醒</v>
       </c>
       <c r="B12" t="str">
-        <v>单次最多导入 20,000 题；每题最多 24 个选项；Excel 文件最大 12 MB。</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>安全提醒</v>
-      </c>
-      <c r="B13" t="str">
         <v>不要在工作簿中填写 GitHub 令牌或其他账号凭据。</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/题库模板.xlsx
+++ b/public/题库模板.xlsx
@@ -1,53 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="题库" sheetId="1" r:id="rId1"/>
-    <sheet name="使用说明" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="题库" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -65,14 +50,83 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -397,258 +451,423 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="46.83203125" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="22.83203125" customWidth="1"/>
-    <col min="5" max="5" width="22.83203125" customWidth="1"/>
-    <col min="6" max="6" width="22.83203125" customWidth="1"/>
-    <col min="7" max="7" width="22.83203125" customWidth="1"/>
-    <col min="8" max="8" width="22.83203125" customWidth="1"/>
-    <col min="9" max="9" width="22.83203125" customWidth="1"/>
-    <col min="10" max="10" width="22.83203125" customWidth="1"/>
-    <col min="11" max="11" width="22.83203125" customWidth="1"/>
-    <col min="12" max="12" width="22.83203125" customWidth="1"/>
+    <col width="46.83203125" customWidth="1" min="1" max="1"/>
+    <col width="10.83203125" customWidth="1" min="2" max="2"/>
+    <col width="12.83203125" customWidth="1" min="3" max="3"/>
+    <col width="22.83203125" customWidth="1" min="4" max="4"/>
+    <col width="22.83203125" customWidth="1" min="5" max="5"/>
+    <col width="22.83203125" customWidth="1" min="6" max="6"/>
+    <col width="22.83203125" customWidth="1" min="7" max="7"/>
+    <col width="22.83203125" customWidth="1" min="8" max="8"/>
+    <col width="22.83203125" customWidth="1" min="9" max="9"/>
+    <col width="22.83203125" customWidth="1" min="10" max="10"/>
+    <col width="22.83203125" customWidth="1" min="11" max="11"/>
+    <col width="22.83203125" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>题干</v>
-      </c>
-      <c r="B1" t="str">
-        <v>题型</v>
-      </c>
-      <c r="C1" t="str">
-        <v>答案</v>
-      </c>
-      <c r="D1" t="str">
-        <v>标签</v>
-      </c>
-      <c r="E1" t="str">
-        <v>A</v>
-      </c>
-      <c r="F1" t="str">
-        <v>B</v>
-      </c>
-      <c r="G1" t="str">
-        <v>C</v>
-      </c>
-      <c r="H1" t="str">
-        <v>D</v>
-      </c>
-      <c r="I1" t="str">
-        <v>E</v>
-      </c>
-      <c r="J1" t="str">
-        <v>F</v>
-      </c>
-      <c r="K1" t="str">
-        <v>G</v>
-      </c>
-      <c r="L1" t="str">
-        <v>H</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>题干</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>题型</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>答案</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>标签</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>解析</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>示例·单选（填好后删）导线的主要作用是什么？</v>
-      </c>
-      <c r="B2" t="str">
-        <v>单选</v>
-      </c>
-      <c r="C2" t="str">
-        <v>A</v>
-      </c>
-      <c r="D2" t="str">
-        <v>基础，示例</v>
-      </c>
-      <c r="E2" t="str">
-        <v>传输电能</v>
-      </c>
-      <c r="F2" t="str">
-        <v>装饰线路</v>
-      </c>
-      <c r="G2" t="str">
-        <v>储存电能</v>
-      </c>
-      <c r="H2" t="str">
-        <v>测量温度</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>示例·单选（填好后删）导线的主要作用是什么？</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>单选</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>基础，示例</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>示例解析：导线的作用是传输电能，其余选项为干扰项。</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>传输电能</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>装饰线路</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>储存电能</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>测量温度</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>示例·多选（填好后删）安全巡视应做到哪些？</v>
-      </c>
-      <c r="B3" t="str">
-        <v>多选</v>
-      </c>
-      <c r="C3" t="str">
-        <v>AB</v>
-      </c>
-      <c r="D3" t="str">
-        <v>安全，示例</v>
-      </c>
-      <c r="E3" t="str">
-        <v>佩戴防护用品</v>
-      </c>
-      <c r="F3" t="str">
-        <v>核对线路编号</v>
-      </c>
-      <c r="G3" t="str">
-        <v>跨越警戒区域</v>
-      </c>
-      <c r="H3" t="str">
-        <v>跳过危险点记录</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>示例·多选（填好后删）安全巡视应做到哪些？</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>多选</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>安全，示例</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>示例解析：安全巡视应核对线路编号并佩戴防护用品。</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>佩戴防护用品</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>核对线路编号</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>跨越警戒区域</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>跳过危险点记录</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>示例·判断（填好后删）巡视前应确认天气和现场风险。</v>
-      </c>
-      <c r="B4" t="str">
-        <v>判断</v>
-      </c>
-      <c r="C4" t="str">
-        <v>A</v>
-      </c>
-      <c r="D4" t="str">
-        <v>安全，示例</v>
-      </c>
-      <c r="E4" t="str">
-        <v>正确</v>
-      </c>
-      <c r="F4" t="str">
-        <v>错误</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>示例·判断（填好后删）巡视前应确认天气和现场风险。</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>判断</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>安全，示例</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>示例解析：巡视前应确认天气与现场风险，确保安全。</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>正确</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>错误</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>示例·计算（填好后删）某量计算结果是多少？</v>
-      </c>
-      <c r="B5" t="str">
-        <v>计算</v>
-      </c>
-      <c r="C5" t="str">
-        <v>12.5</v>
-      </c>
-      <c r="D5" t="str">
-        <v>计算，示例</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>示例·计算（填好后删）某量计算结果是多少？</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>计算</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>12.5</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>计算，示例</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>示例解析：计算题按标准数值判定，误差见配置页。</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
-    <col min="2" max="2" width="110.83203125" customWidth="1"/>
+    <col width="18.83203125" customWidth="1" min="1" max="1"/>
+    <col width="110.83203125" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>拾卷 · 题库 Excel 模板使用说明</v>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>拾卷 · 题库 Excel 模板使用说明</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>适用项目</v>
-      </c>
-      <c r="B2" t="str">
-        <v>拾卷（exam-study-app）本地优先刷题 PWA</v>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>适用项目</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>拾卷（exam-study-app）本地优先刷题 PWA</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>导入步骤</v>
-      </c>
-      <c r="B3" t="str">
-        <v>1. 复制本模板；2. 删除题库页全部示例行；3. 按列填写；4. 将文件命名为送电线路工-初级工/中级工/高级工/技师.xlsx；5. 在题库页点击导入 Excel。</v>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>导入步骤</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1. 复制本模板；2. 删除题库页全部示例行；3. 按列填写；4. 将文件命名为送电线路工-初级工/中级工/高级工/技师.xlsx；5. 在题库页点击导入 Excel。</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>题干</v>
-      </c>
-      <c r="B4" t="str">
-        <v>必填。支持普通文字，以及 $...$ 行内公式和 $$...$$ 独立公式。</v>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>题干</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>必填。支持普通文字，以及 $...$ 行内公式和 $$...$$ 独立公式。</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>题型</v>
-      </c>
-      <c r="B5" t="str">
-        <v>必填，只能填写：单选、多选、判断、计算。</v>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>题型</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>必填，只能填写：单选、多选、判断、计算。</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>答案</v>
-      </c>
-      <c r="B6" t="str">
-        <v>单选填一个字母；多选填多个字母（如 AC）；判断填 A/正确 或 B/错误；计算题填标准数值（如 12.5、-3、1e6）。</v>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>答案</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>单选填一个字母；多选填多个字母（如 AC）；判断填 A/正确 或 B/错误；计算题填标准数值（如 12.5、-3、1e6）。</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <v>标签</v>
-      </c>
-      <c r="B7" t="str">
-        <v>可选。多个标签使用中文逗号、英文逗号或顿号分隔。</v>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>标签</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>可选。多个标签使用中文逗号、英文逗号或顿号分隔。</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
-        <v>选项</v>
-      </c>
-      <c r="B8" t="str">
-        <v>单选、多选、判断题从 A 列开始连续填写，不得断列；判断题必须依次为“正确、错误”。计算题不要填写选项。</v>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>解析</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>可选。该题的个人解析，导入时会写回为本机笔记（不会覆盖已有解析）。</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
-        <v>计算题误差</v>
-      </c>
-      <c r="B9" t="str">
-        <v>计算题按配置页中的“计算题允许误差”判定，使用相对误差百分比；标准答案为 0 时按同一百分比折算为绝对误差。</v>
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>选项</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>单选、多选、判断题的选项从「解析」右侧的 A 列开始连续填写，不得断列；判断题必须依次为“正确、错误”。计算题不要填写选项。</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
-        <v>图片题</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Excel 只导入纯文字题。导入后请在题目编辑器中选择本机图片并插入到题干或选项的任意位置；图片会作为私有资产同步。</v>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>计算题误差</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>计算题按配置页中的“计算题允许误差”判定，使用相对误差百分比；标准答案为 0 时按同一百分比折算为绝对误差。</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
-        <v>限制</v>
-      </c>
-      <c r="B11" t="str">
-        <v>单次最多导入 20,000 题；每题最多 24 个选项；Excel 文件最大 12 MB。</v>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>图片题</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Excel 只导入纯文字题。导入后请在题目编辑器中选择本机图片并插入到题干或选项的任意位置；图片会作为私有资产同步。</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
-        <v>安全提醒</v>
-      </c>
-      <c r="B12" t="str">
-        <v>不要在工作簿中填写 GitHub 令牌或其他账号凭据。</v>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>限制</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>单次最多导入 20,000 题；每题最多 24 个选项；Excel 文件最大 12 MB。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>安全提醒</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>不要在工作簿中填写 GitHub 令牌或其他账号凭据。</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B12"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/题库模板.xlsx
+++ b/public/题库模板.xlsx
@@ -45,20 +45,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
-    <col min="1" max="1" width="46" customWidth="1"/>
+    <col min="1" max="1" width="58" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="28" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="34" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
     <col min="9" max="9" width="22" customWidth="1"/>
     <col min="10" max="10" width="22" customWidth="1"/>
     <col min="11" max="11" width="22" customWidth="1"/>
     <col min="12" max="12" width="22" customWidth="1"/>
     <col min="13" max="13" width="22" customWidth="1"/>
-    <col min="14" max="14" width="28" customWidth="1"/>
+    <col min="14" max="14" width="22" customWidth="1"/>
+    <col min="15" max="15" width="22" customWidth="1"/>
+    <col min="16" max="16" width="22" customWidth="1"/>
+    <col min="17" max="17" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -74,60 +77,75 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>答案</t>
+          <t>标签</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>标签</t>
+          <t>解析</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>解析</t>
+          <t>答案1</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>答案2</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>答案3</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>答案4</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>图片1</t>
         </is>
@@ -146,35 +164,35 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>基础，示例</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>示例解析：导线的作用是传输电能，其余选项为干扰项。</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>基础，示例</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>示例解析：导线的作用是传输电能，其余选项为干扰项。</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>传输电能</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>装饰线路</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>储存电能</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>测量温度</t>
         </is>
@@ -193,35 +211,35 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>安全，示例</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>示例解析：安全巡视应核对线路编号并佩戴防护用品。</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>AB</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>安全，示例</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>示例解析：安全巡视应核对线路编号并佩戴防护用品。</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>佩戴防护用品</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>核对线路编号</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>跨越警戒区域</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>跳过危险点记录</t>
         </is>
@@ -240,25 +258,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>安全，示例</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>示例解析：巡视前应确认天气与现场风险，确保安全。</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>安全，示例</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>示例解析：巡视前应确认天气与现场风险，确保安全。</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>正确</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>错误</t>
         </is>
@@ -267,7 +285,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>示例·计算（填好后删）某量计算结果是多少？</t>
+          <t>示例·单空计算（填好后删）某量计算结果为【空1】。</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -277,67 +295,99 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>计算，示例</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>示例解析：答案1 对应题干中的【空1】。</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>12.5</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>计算，示例</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>示例解析：计算题按标准数值判定，误差见配置页。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="152" customHeight="1">
+    </row>
+    <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>示例·多空计算（填好后删）将 R=8Ω 的电阻和容抗 XC=6Ω 的电容器串联，接在频率为 f=50Hz、电压为 U=110V 的正弦交流电源上。电路中的电流为【空1】A，所消耗的有功功率为【空2】W。</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>计算</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>计算，多空，示例</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>示例解析：两个填空分别对应答案1和答案2，每个空独立按误差比例判定。</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>968.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="152" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>示例·图片单选（填好后删）图中图标对应哪个应用？【图1】</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>单选</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>图片，示例</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>示例解析：图片1 嵌入在本行最后一列，题干中的【图1】决定图片显示位置。</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>图片，示例</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>示例解析：图片1 嵌入在本行最后一列，题干中的【图1】决定图片显示位置。</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>拾卷</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>浏览器</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>相册</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>日历</t>
         </is>
       </c>
-      <c r="N6" t="str">
+      <c r="Q7" t="str">
         <f>_xlfn.DISPIMG("ID_TEMPLATE_SHIJUAN_APP_ICON",1)</f>
         <v>=DISPIMG("ID_TEMPLATE_SHIJUAN_APP_ICON",1)</v>
       </c>
@@ -392,7 +442,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>必填。支持普通文字、$...$ 行内公式、$$...$$ 独立公式，以及【图1】【图2】等图片占位符。</t>
+          <t>必填。支持普通文字、公式、【图1】等图片占位符，以及计算题的【空1】【空2】等填空占位符。</t>
         </is>
       </c>
     </row>
@@ -411,12 +461,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>答案</t>
+          <t>答案列</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>单选填一个字母；多选填多个字母（如 AC）；判断填 A/正确 或 B/错误；计算题填标准数值（如 12.5、-3、1e6）。</t>
+          <t>所有题至少填写答案1。单选、多选、判断只填写答案1；计算题按填空顺序分别填写答案1、答案2…，答案列之间不得留空。</t>
         </is>
       </c>
     </row>
@@ -452,77 +502,89 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>单选、多选、判断题的选项从「解析」右侧的 A 列开始连续填写，不得断列；判断题必须依次为“正确、错误”。计算题不要填写选项。</t>
+          <t>单选、多选、判断题的选项从答案列右侧的 A 列开始连续填写，不得断列；判断题必须依次为“正确、错误”。计算题不要填写选项。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>计算题误差</t>
+          <t>多空计算题</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>计算题按配置页中的“计算题允许误差”判定，使用相对误差百分比；标准答案为 0 时按同一百分比折算为绝对误差。</t>
+          <t>题干必须从【空1】开始连续编号，每个编号只能出现一次；答案1对应空1、答案2对应空2。每个空独立应用误差规则，全部正确才算整题正确。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>图片题</t>
+          <t>计算题误差</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>支持题干图片和选项图片。先在题干或选项文字中写【图1】【图2】等占位符，再把对应图片按编号放入本行末尾的“图片1”“图片2”列。每一题都从图1重新编号。</t>
+          <t>非零标准答案按相对误差百分比判定；标准答案为0时改用绝对误差，允许偏差=误差百分比÷100。例如1%时，-0.01至0.01均正确。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>插入图片</t>
+          <t>图片题</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>推荐使用 WPS 的“插入图片→嵌入单元格”，并保持图片列位于全部选项列之后且从“图片1”连续编号。不要填写本机路径或网络图片地址。</t>
+          <t>支持题干图片和选项图片。先在题干或选项文字中写【图1】【图2】等占位符，再把对应图片按编号放入本行末尾的“图片1”“图片2”列。每一题都从图1重新编号。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>兼容提示</t>
+          <t>插入图片</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>模板图片采用 WPS DISPIMG 单元格图片格式；WPS 可正常查看和编辑。部分 Microsoft Excel 版本可能显示 #NAME?，但请勿删除图片列或公式，以免导入时丢图。</t>
+          <t>推荐使用 WPS 的“插入图片→嵌入单元格”，并保持图片列位于全部选项列之后且从“图片1”连续编号。不要填写本机路径或网络图片地址。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>限制</t>
+          <t>兼容提示</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>单次最多导入 20,000 题；每题最多 24 个选项、12 张图片；Excel 文件最大 12 MB。</t>
+          <t>模板图片采用 WPS DISPIMG 单元格图片格式；WPS 可正常查看和编辑。部分 Microsoft Excel 版本可能显示 #NAME?，但请勿删除图片列或公式，以免导入时丢图。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>限制</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>单次最多导入 20,000 题；每题最多 12 个填空、24 个选项、12 张图片；Excel 文件最大 12 MB。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>安全提醒</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>图片会作为本地私有资产导入并随私有仓库同步；不要在工作簿中填写 GitHub 令牌或其他账号凭据。</t>
         </is>

--- a/public/题库模板.xlsx
+++ b/public/题库模板.xlsx
@@ -51,17 +51,11 @@
     <col min="4" max="4" width="34" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
     <col min="9" max="9" width="22" customWidth="1"/>
     <col min="10" max="10" width="22" customWidth="1"/>
-    <col min="11" max="11" width="22" customWidth="1"/>
-    <col min="12" max="12" width="22" customWidth="1"/>
-    <col min="13" max="13" width="22" customWidth="1"/>
-    <col min="14" max="14" width="22" customWidth="1"/>
-    <col min="15" max="15" width="22" customWidth="1"/>
-    <col min="16" max="16" width="22" customWidth="1"/>
-    <col min="17" max="17" width="28" customWidth="1"/>
+    <col min="11" max="11" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -97,55 +91,25 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>答案3</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>答案4</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
         <is>
           <t>图片1</t>
         </is>
@@ -177,22 +141,22 @@
           <t>A</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>传输电能</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>装饰线路</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>传输电能</t>
+          <t>储存电能</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
-        <is>
-          <t>装饰线路</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>储存电能</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
         <is>
           <t>测量温度</t>
         </is>
@@ -224,22 +188,22 @@
           <t>AB</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>佩戴防护用品</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>核对线路编号</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>佩戴防护用品</t>
+          <t>跨越警戒区域</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
-        <is>
-          <t>核对线路编号</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>跨越警戒区域</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
         <is>
           <t>跳过危险点记录</t>
         </is>
@@ -271,12 +235,12 @@
           <t>A</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>正确</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>错误</t>
         </is>
@@ -367,29 +331,115 @@
           <t>A</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>拾卷</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>浏览器</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>拾卷</t>
+          <t>相册</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>浏览器</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>相册</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
           <t>日历</t>
         </is>
       </c>
-      <c r="Q7" t="str">
+      <c r="K7" t="str">
         <f>_xlfn.DISPIMG("ID_TEMPLATE_SHIJUAN_APP_ICON",1)</f>
         <v>=DISPIMG("ID_TEMPLATE_SHIJUAN_APP_ICON",1)</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>示例·单空填空（填好后删）输电线路的主要作用是【空1】。</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>填空，示例</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>示例解析：同一空允许多个等价答案时，在答案单元格内用 || 分隔。</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>传输电能||输送电能</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>示例·多空填空（填好后删）三相交流电中，相邻两相电动势的相位差为【空1】°，我国电力系统工频为【空2】Hz。</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>填空</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>填空，多空，示例</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>示例解析：答案1对应空1、答案2对应空2；每个空可分别设置多个等价答案。</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>50||50赫兹</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>示例·简答（填好后删）简述输电线路巡视前应完成的主要安全准备。</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>简答</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>简答，安全，示例</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>示例解析：简答题由答题者对照参考答案自行判定正确或错误。</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>确认天气和现场风险，核对线路及作业信息，准备并检查必要的安全防护用品和巡视工具。</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -442,7 +492,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>必填。支持普通文字、公式、【图1】等图片占位符，以及计算题的【空1】【空2】等填空占位符。</t>
+          <t>必填。支持普通文字、公式、【图1】等图片占位符，以及计算题/填空题的【空1】【空2】等答题占位符。</t>
         </is>
       </c>
     </row>
@@ -454,7 +504,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>必填，只能填写：单选、多选、判断、计算。</t>
+          <t>必填，只能填写：单选、多选、判断、计算、填空、简答。</t>
         </is>
       </c>
     </row>
@@ -466,7 +516,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>所有题至少填写答案1。单选、多选、判断只填写答案1；计算题按填空顺序分别填写答案1、答案2…，答案列之间不得留空。</t>
+          <t>模板只预留答案1、答案2两列。所有题至少填写答案1；单选、多选、判断、简答只填写答案1；计算题、填空题按空位顺序填写答案1、答案2……。如需更多空位，请在选项A之前继续插入答案3、答案4……，答案/填空最多 12 列，且答案列之间不得留空。</t>
         </is>
       </c>
     </row>
@@ -502,7 +552,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>单选、多选、判断题的选项从答案列右侧的 A 列开始连续填写，不得断列；判断题必须依次为“正确、错误”。计算题不要填写选项。</t>
+          <t>模板只预留 A、B、C、D 四列。只有单选、多选、判断题填写选项；需要更多选项时可在图片列之前继续按 E、F、G……连续增加。判断题必须依次为“正确、错误”。计算、填空、简答题不要填写选项。</t>
         </is>
       </c>
     </row>
@@ -533,58 +583,82 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>图片题</t>
+          <t>填空题</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>支持题干图片和选项图片。先在题干或选项文字中写【图1】【图2】等占位符，再把对应图片按编号放入本行末尾的“图片1”“图片2”列。每一题都从图1重新编号。</t>
+          <t>答案1对应第1空、答案2对应第2空……；同一空有多个可接受答案时，在同一个答案单元格内用 || 分隔，例如“电流||电流强度”。答案比较会忽略首尾空格并统一大小写/全半角。填空题不填写选项。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>插入图片</t>
+          <t>简答题</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>推荐使用 WPS 的“插入图片→嵌入单元格”，并保持图片列位于全部选项列之后且从“图片1”连续编号。不要填写本机路径或网络图片地址。</t>
+          <t>只填写答案1作为参考答案，其余答案列与全部选项列留空。练习时先作答，再对照参考答案自行判定正确或错误。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>兼容提示</t>
+          <t>图片题</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>模板图片采用 WPS DISPIMG 单元格图片格式；WPS 可正常查看和编辑。部分 Microsoft Excel 版本可能显示 #NAME?，但请勿删除图片列或公式，以免导入时丢图。</t>
+          <t>支持题干图片和选项图片。先在题干或选项文字中写【图1】【图2】等占位符，再把对应图片按编号放入本行末尾的“图片1”“图片2”列。每一题都从图1重新编号。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>限制</t>
+          <t>插入图片</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>单次最多导入 20,000 题；每题最多 12 个填空、24 个选项、12 张图片；Excel 文件最大 12 MB。</t>
+          <t>推荐使用 WPS 的“插入图片→嵌入单元格”，并保持图片列位于全部选项列之后且从“图片1”连续编号。不要填写本机路径或网络图片地址。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>兼容提示</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>模板图片继续使用原模板同一张拾卷图标，并采用 WPS DISPIMG 单元格图片格式；WPS 可正常查看和编辑。部分 Microsoft Excel 版本可能显示 #NAME?，但请勿删除图片列或公式，以免导入时丢图。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>限制</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>模板仅预留 2 个答案列和 4 个选项列；系统答案/填空上限为 12 列。需要更多列时按上述规则连续扩展。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>安全提醒</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>图片会作为本地私有资产导入并随私有仓库同步；不要在工作簿中填写 GitHub 令牌或其他账号凭据。</t>
         </is>
